--- a/artfynd/S 628-2025 artfynd.xlsx
+++ b/artfynd/S 628-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54834</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83461630</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83461635</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95972127</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1251,6 +1276,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92691097</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92691095</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1494,6 +1529,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107083901</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1609,6 +1649,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107083903</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1728,6 +1773,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107083900</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1843,6 +1893,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106049875</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1940,6 +1995,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/30527</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2051,6 +2111,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125327828</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2158,6 +2223,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94140431</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2273,6 +2343,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107083904</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2392,6 +2467,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467651</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2511,6 +2591,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92691102</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2612,6 +2697,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87369151</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2731,6 +2821,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92691099</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2846,6 +2941,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106049888</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2961,6 +3061,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106049892</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3068,6 +3173,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121970852</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3175,6 +3285,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95351808</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3285,6 +3400,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80002161</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3386,6 +3506,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103252750</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3504,6 +3629,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93175983</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3622,6 +3752,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93175988</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3741,6 +3876,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105545837</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3860,6 +4000,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105545823</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3975,6 +4120,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105545829</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4091,8 +4241,45 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63432965</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>